--- a/data/Wellness.xlsx
+++ b/data/Wellness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C880DB30-7BD3-E748-A647-473F20D9E6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD316AA-0EDB-CC4F-9B96-0F9C9909C893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{1A9C3045-D9B1-2C40-BB1C-55E131BFBA85}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="161">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -507,6 +507,18 @@
   </si>
   <si>
     <t>Coups</t>
+  </si>
+  <si>
+    <t>Fessier</t>
+  </si>
+  <si>
+    <t>Ischio adduct </t>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <t>Fatigué </t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D0374B-10DC-0242-BBAD-60229EC6B28B}">
-  <dimension ref="A1:I919"/>
+  <dimension ref="A1:I945"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
@@ -27495,7 +27507,7 @@
         <v>8</v>
       </c>
       <c r="I900">
-        <f t="shared" ref="I900:I919" si="14">C900*D900</f>
+        <f t="shared" ref="I900:I945" si="14">C900*D900</f>
         <v>560</v>
       </c>
     </row>
@@ -28047,6 +28059,766 @@
       <c r="I919">
         <f t="shared" si="14"/>
         <v>350</v>
+      </c>
+    </row>
+    <row r="920" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A920" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B920" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C920" s="1">
+        <v>70</v>
+      </c>
+      <c r="D920" s="1">
+        <v>5</v>
+      </c>
+      <c r="E920" s="1">
+        <v>7</v>
+      </c>
+      <c r="F920" s="1">
+        <v>6</v>
+      </c>
+      <c r="G920" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H920" s="1">
+        <v>3</v>
+      </c>
+      <c r="I920">
+        <f t="shared" si="14"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="921" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A921" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B921" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C921" s="1">
+        <v>70</v>
+      </c>
+      <c r="D921" s="1">
+        <v>6</v>
+      </c>
+      <c r="E921" s="1">
+        <v>3</v>
+      </c>
+      <c r="F921" s="1">
+        <v>2</v>
+      </c>
+      <c r="G921" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H921" s="1">
+        <v>8</v>
+      </c>
+      <c r="I921">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="922" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A922" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B922" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C922" s="1">
+        <v>70</v>
+      </c>
+      <c r="D922" s="1">
+        <v>5</v>
+      </c>
+      <c r="E922" s="1">
+        <v>4</v>
+      </c>
+      <c r="F922" s="1">
+        <v>3</v>
+      </c>
+      <c r="G922" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H922" s="1">
+        <v>8</v>
+      </c>
+      <c r="I922">
+        <f t="shared" si="14"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="923" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A923" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B923" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C923" s="1">
+        <v>70</v>
+      </c>
+      <c r="D923" s="1">
+        <v>4</v>
+      </c>
+      <c r="E923" s="1">
+        <v>5</v>
+      </c>
+      <c r="F923" s="1">
+        <v>0</v>
+      </c>
+      <c r="G923" s="2"/>
+      <c r="H923" s="1">
+        <v>9</v>
+      </c>
+      <c r="I923">
+        <f t="shared" si="14"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="924" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A924" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B924" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C924" s="1">
+        <v>70</v>
+      </c>
+      <c r="D924" s="1">
+        <v>4</v>
+      </c>
+      <c r="E924" s="1">
+        <v>4</v>
+      </c>
+      <c r="F924" s="1">
+        <v>3</v>
+      </c>
+      <c r="G924" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H924" s="1">
+        <v>2</v>
+      </c>
+      <c r="I924">
+        <f t="shared" si="14"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="925" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A925" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B925" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C925" s="1">
+        <v>70</v>
+      </c>
+      <c r="D925" s="1">
+        <v>7</v>
+      </c>
+      <c r="E925" s="1">
+        <v>7</v>
+      </c>
+      <c r="F925" s="1">
+        <v>0</v>
+      </c>
+      <c r="G925" s="2"/>
+      <c r="H925" s="1">
+        <v>9</v>
+      </c>
+      <c r="I925">
+        <f t="shared" si="14"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="926" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A926" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B926" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C926" s="1">
+        <v>70</v>
+      </c>
+      <c r="D926" s="1">
+        <v>5</v>
+      </c>
+      <c r="E926" s="1">
+        <v>0</v>
+      </c>
+      <c r="F926" s="1">
+        <v>0</v>
+      </c>
+      <c r="G926" s="2"/>
+      <c r="H926" s="1">
+        <v>9</v>
+      </c>
+      <c r="I926">
+        <f t="shared" si="14"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="927" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A927" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B927" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C927" s="1">
+        <v>70</v>
+      </c>
+      <c r="D927" s="1">
+        <v>7</v>
+      </c>
+      <c r="E927" s="1">
+        <v>6</v>
+      </c>
+      <c r="F927" s="1">
+        <v>5</v>
+      </c>
+      <c r="G927" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H927" s="1">
+        <v>8</v>
+      </c>
+      <c r="I927">
+        <f t="shared" si="14"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="928" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A928" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B928" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C928" s="1">
+        <v>70</v>
+      </c>
+      <c r="D928" s="1">
+        <v>4</v>
+      </c>
+      <c r="E928" s="1">
+        <v>3</v>
+      </c>
+      <c r="F928" s="1">
+        <v>0</v>
+      </c>
+      <c r="G928" s="2"/>
+      <c r="H928" s="1">
+        <v>8</v>
+      </c>
+      <c r="I928">
+        <f t="shared" si="14"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="929" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A929" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B929" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C929" s="1">
+        <v>70</v>
+      </c>
+      <c r="D929" s="1">
+        <v>6</v>
+      </c>
+      <c r="E929" s="1">
+        <v>7</v>
+      </c>
+      <c r="F929" s="1">
+        <v>0</v>
+      </c>
+      <c r="G929" s="2"/>
+      <c r="H929" s="1">
+        <v>3</v>
+      </c>
+      <c r="I929">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="930" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A930" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B930" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C930" s="1">
+        <v>70</v>
+      </c>
+      <c r="D930" s="1">
+        <v>4</v>
+      </c>
+      <c r="E930" s="1">
+        <v>3</v>
+      </c>
+      <c r="F930" s="1">
+        <v>0</v>
+      </c>
+      <c r="G930" s="2"/>
+      <c r="H930" s="1">
+        <v>5</v>
+      </c>
+      <c r="I930">
+        <f t="shared" si="14"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="931" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A931" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B931" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C931" s="1">
+        <v>70</v>
+      </c>
+      <c r="D931" s="1">
+        <v>6</v>
+      </c>
+      <c r="E931" s="1">
+        <v>7</v>
+      </c>
+      <c r="F931" s="1">
+        <v>5</v>
+      </c>
+      <c r="G931" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H931" s="1">
+        <v>7</v>
+      </c>
+      <c r="I931">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="932" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A932" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B932" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C932" s="1">
+        <v>70</v>
+      </c>
+      <c r="D932" s="1">
+        <v>6</v>
+      </c>
+      <c r="E932" s="1">
+        <v>9</v>
+      </c>
+      <c r="F932" s="1">
+        <v>6</v>
+      </c>
+      <c r="G932" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H932" s="1">
+        <v>8</v>
+      </c>
+      <c r="I932">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="933" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A933" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B933" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C933" s="1">
+        <v>70</v>
+      </c>
+      <c r="D933" s="1">
+        <v>6</v>
+      </c>
+      <c r="E933" s="1">
+        <v>8</v>
+      </c>
+      <c r="F933" s="1">
+        <v>4</v>
+      </c>
+      <c r="G933" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H933" s="1">
+        <v>0</v>
+      </c>
+      <c r="I933">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="934" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A934" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B934" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C934" s="1">
+        <v>70</v>
+      </c>
+      <c r="D934" s="1">
+        <v>4</v>
+      </c>
+      <c r="E934" s="1">
+        <v>3</v>
+      </c>
+      <c r="F934" s="1">
+        <v>2</v>
+      </c>
+      <c r="G934" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H934" s="1">
+        <v>1</v>
+      </c>
+      <c r="I934">
+        <f t="shared" si="14"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="935" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A935" s="3">
+        <v>46085</v>
+      </c>
+      <c r="B935" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C935" s="1">
+        <v>70</v>
+      </c>
+      <c r="D935" s="1">
+        <v>5</v>
+      </c>
+      <c r="E935" s="1">
+        <v>6</v>
+      </c>
+      <c r="F935" s="1">
+        <v>4</v>
+      </c>
+      <c r="G935" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H935" s="1">
+        <v>4</v>
+      </c>
+      <c r="I935">
+        <f t="shared" si="14"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="936" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A936" s="3">
+        <v>46085</v>
+      </c>
+      <c r="B936" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C936" s="1">
+        <v>70</v>
+      </c>
+      <c r="D936" s="1">
+        <v>5</v>
+      </c>
+      <c r="E936" s="1">
+        <v>5</v>
+      </c>
+      <c r="F936" s="1">
+        <v>2</v>
+      </c>
+      <c r="G936" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H936" s="1">
+        <v>5</v>
+      </c>
+      <c r="I936">
+        <f t="shared" si="14"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="937" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A937" s="3">
+        <v>46085</v>
+      </c>
+      <c r="B937" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C937" s="1">
+        <v>70</v>
+      </c>
+      <c r="D937" s="1">
+        <v>7</v>
+      </c>
+      <c r="E937" s="1">
+        <v>6</v>
+      </c>
+      <c r="F937" s="1">
+        <v>4</v>
+      </c>
+      <c r="G937" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H937" s="1">
+        <v>6</v>
+      </c>
+      <c r="I937">
+        <f t="shared" si="14"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="938" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A938" s="3">
+        <v>46085</v>
+      </c>
+      <c r="B938" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C938" s="1">
+        <v>70</v>
+      </c>
+      <c r="D938" s="1">
+        <v>6</v>
+      </c>
+      <c r="E938" s="1">
+        <v>8</v>
+      </c>
+      <c r="F938" s="1">
+        <v>0</v>
+      </c>
+      <c r="G938" s="2"/>
+      <c r="H938" s="1">
+        <v>8</v>
+      </c>
+      <c r="I938">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="939" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A939" s="3">
+        <v>46085</v>
+      </c>
+      <c r="B939" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C939" s="1">
+        <v>70</v>
+      </c>
+      <c r="D939" s="1">
+        <v>6</v>
+      </c>
+      <c r="E939" s="1">
+        <v>5</v>
+      </c>
+      <c r="F939" s="1">
+        <v>1</v>
+      </c>
+      <c r="G939" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H939" s="1">
+        <v>5</v>
+      </c>
+      <c r="I939">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="940" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A940" s="3">
+        <v>46085</v>
+      </c>
+      <c r="B940" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C940" s="1">
+        <v>70</v>
+      </c>
+      <c r="D940" s="1">
+        <v>4</v>
+      </c>
+      <c r="E940" s="1">
+        <v>5</v>
+      </c>
+      <c r="F940" s="1">
+        <v>1</v>
+      </c>
+      <c r="G940" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H940" s="1">
+        <v>2</v>
+      </c>
+      <c r="I940">
+        <f t="shared" si="14"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="941" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A941" s="3">
+        <v>46085</v>
+      </c>
+      <c r="B941" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C941" s="1">
+        <v>70</v>
+      </c>
+      <c r="D941" s="1">
+        <v>4</v>
+      </c>
+      <c r="E941" s="1">
+        <v>4</v>
+      </c>
+      <c r="F941" s="1">
+        <v>4</v>
+      </c>
+      <c r="G941" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H941" s="1">
+        <v>4</v>
+      </c>
+      <c r="I941">
+        <f t="shared" si="14"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="942" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A942" s="3">
+        <v>46085</v>
+      </c>
+      <c r="B942" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C942" s="1">
+        <v>70</v>
+      </c>
+      <c r="D942" s="1">
+        <v>7</v>
+      </c>
+      <c r="E942" s="1">
+        <v>7</v>
+      </c>
+      <c r="F942" s="1">
+        <v>0</v>
+      </c>
+      <c r="G942" s="2"/>
+      <c r="H942" s="1">
+        <v>7</v>
+      </c>
+      <c r="I942">
+        <f t="shared" si="14"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="943" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A943" s="3">
+        <v>46085</v>
+      </c>
+      <c r="B943" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C943" s="1">
+        <v>70</v>
+      </c>
+      <c r="D943" s="1">
+        <v>6</v>
+      </c>
+      <c r="E943" s="1">
+        <v>7</v>
+      </c>
+      <c r="F943" s="1">
+        <v>0</v>
+      </c>
+      <c r="G943" s="2"/>
+      <c r="H943" s="1">
+        <v>4</v>
+      </c>
+      <c r="I943">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="944" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A944" s="3">
+        <v>46085</v>
+      </c>
+      <c r="B944" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C944" s="1">
+        <v>70</v>
+      </c>
+      <c r="D944" s="1">
+        <v>7</v>
+      </c>
+      <c r="E944" s="1">
+        <v>10</v>
+      </c>
+      <c r="F944" s="1">
+        <v>0</v>
+      </c>
+      <c r="G944" s="2"/>
+      <c r="H944" s="1">
+        <v>8</v>
+      </c>
+      <c r="I944">
+        <f t="shared" si="14"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="945" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A945" s="3">
+        <v>46085</v>
+      </c>
+      <c r="B945" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C945" s="1">
+        <v>70</v>
+      </c>
+      <c r="D945" s="1">
+        <v>6</v>
+      </c>
+      <c r="E945" s="1">
+        <v>8</v>
+      </c>
+      <c r="F945" s="1">
+        <v>4</v>
+      </c>
+      <c r="G945" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H945" s="1">
+        <v>5</v>
+      </c>
+      <c r="I945">
+        <f t="shared" si="14"/>
+        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/data/Wellness.xlsx
+++ b/data/Wellness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD316AA-0EDB-CC4F-9B96-0F9C9909C893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6E6C04-1C33-924B-A3EF-497C29B72667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{1A9C3045-D9B1-2C40-BB1C-55E131BFBA85}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="162">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -519,6 +519,9 @@
   </si>
   <si>
     <t>Fatigué </t>
+  </si>
+  <si>
+    <t>Tibia </t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D0374B-10DC-0242-BBAD-60229EC6B28B}">
-  <dimension ref="A1:I945"/>
+  <dimension ref="A1:I966"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
@@ -27507,7 +27510,7 @@
         <v>8</v>
       </c>
       <c r="I900">
-        <f t="shared" ref="I900:I945" si="14">C900*D900</f>
+        <f t="shared" ref="I900:I963" si="14">C900*D900</f>
         <v>560</v>
       </c>
     </row>
@@ -28819,6 +28822,614 @@
       <c r="I945">
         <f t="shared" si="14"/>
         <v>420</v>
+      </c>
+    </row>
+    <row r="946" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A946" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B946" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C946" s="1">
+        <v>70</v>
+      </c>
+      <c r="D946" s="1">
+        <v>7</v>
+      </c>
+      <c r="E946" s="1">
+        <v>5</v>
+      </c>
+      <c r="F946" s="1">
+        <v>0</v>
+      </c>
+      <c r="G946" s="2"/>
+      <c r="H946" s="1">
+        <v>7</v>
+      </c>
+      <c r="I946">
+        <f t="shared" si="14"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="947" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A947" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B947" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C947" s="1">
+        <v>70</v>
+      </c>
+      <c r="D947" s="1">
+        <v>7</v>
+      </c>
+      <c r="E947" s="1">
+        <v>4</v>
+      </c>
+      <c r="F947" s="1">
+        <v>3</v>
+      </c>
+      <c r="G947" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H947" s="1">
+        <v>7</v>
+      </c>
+      <c r="I947">
+        <f t="shared" si="14"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="948" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A948" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B948" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C948" s="1">
+        <v>70</v>
+      </c>
+      <c r="D948" s="1">
+        <v>6</v>
+      </c>
+      <c r="E948" s="1">
+        <v>4</v>
+      </c>
+      <c r="F948" s="1">
+        <v>0</v>
+      </c>
+      <c r="G948" s="2"/>
+      <c r="H948" s="1">
+        <v>6</v>
+      </c>
+      <c r="I948">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="949" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A949" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B949" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C949" s="1">
+        <v>70</v>
+      </c>
+      <c r="D949" s="1">
+        <v>7</v>
+      </c>
+      <c r="E949" s="1">
+        <v>5</v>
+      </c>
+      <c r="F949" s="1">
+        <v>7</v>
+      </c>
+      <c r="G949" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H949" s="1">
+        <v>9</v>
+      </c>
+      <c r="I949">
+        <f t="shared" si="14"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="950" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A950" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B950" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C950" s="1">
+        <v>70</v>
+      </c>
+      <c r="D950" s="1">
+        <v>7</v>
+      </c>
+      <c r="E950" s="1">
+        <v>7</v>
+      </c>
+      <c r="F950" s="1">
+        <v>0</v>
+      </c>
+      <c r="G950" s="2"/>
+      <c r="H950" s="1">
+        <v>3</v>
+      </c>
+      <c r="I950">
+        <f t="shared" si="14"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="951" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A951" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B951" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C951" s="1">
+        <v>70</v>
+      </c>
+      <c r="D951" s="1">
+        <v>7</v>
+      </c>
+      <c r="E951" s="1">
+        <v>9</v>
+      </c>
+      <c r="F951" s="1">
+        <v>3</v>
+      </c>
+      <c r="G951" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H951" s="1">
+        <v>0</v>
+      </c>
+      <c r="I951">
+        <f t="shared" si="14"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="952" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A952" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B952" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C952" s="1">
+        <v>70</v>
+      </c>
+      <c r="D952" s="1">
+        <v>9</v>
+      </c>
+      <c r="E952" s="1">
+        <v>6</v>
+      </c>
+      <c r="F952" s="1">
+        <v>0</v>
+      </c>
+      <c r="G952" s="2"/>
+      <c r="H952" s="1">
+        <v>10</v>
+      </c>
+      <c r="I952">
+        <f t="shared" si="14"/>
+        <v>630</v>
+      </c>
+    </row>
+    <row r="953" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A953" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B953" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C953" s="1">
+        <v>70</v>
+      </c>
+      <c r="D953" s="1">
+        <v>7</v>
+      </c>
+      <c r="E953" s="1">
+        <v>3</v>
+      </c>
+      <c r="F953" s="1">
+        <v>5</v>
+      </c>
+      <c r="G953" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H953" s="1">
+        <v>4</v>
+      </c>
+      <c r="I953">
+        <f t="shared" si="14"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="954" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A954" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B954" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C954" s="1">
+        <v>70</v>
+      </c>
+      <c r="D954" s="1">
+        <v>5</v>
+      </c>
+      <c r="E954" s="1">
+        <v>7</v>
+      </c>
+      <c r="F954" s="1">
+        <v>7</v>
+      </c>
+      <c r="G954" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H954" s="1">
+        <v>10</v>
+      </c>
+      <c r="I954">
+        <f t="shared" si="14"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="955" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A955" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B955" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C955" s="1">
+        <v>70</v>
+      </c>
+      <c r="D955" s="1">
+        <v>6</v>
+      </c>
+      <c r="E955" s="1">
+        <v>6</v>
+      </c>
+      <c r="F955" s="1">
+        <v>1</v>
+      </c>
+      <c r="G955" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H955" s="1">
+        <v>7</v>
+      </c>
+      <c r="I955">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="956" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A956" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B956" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C956" s="1">
+        <v>70</v>
+      </c>
+      <c r="D956" s="1">
+        <v>8</v>
+      </c>
+      <c r="E956" s="1">
+        <v>6</v>
+      </c>
+      <c r="F956" s="1">
+        <v>0</v>
+      </c>
+      <c r="G956" s="2"/>
+      <c r="H956" s="1">
+        <v>9</v>
+      </c>
+      <c r="I956">
+        <f t="shared" si="14"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="957" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A957" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B957" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C957" s="1">
+        <v>70</v>
+      </c>
+      <c r="D957" s="1">
+        <v>7</v>
+      </c>
+      <c r="E957" s="1">
+        <v>7</v>
+      </c>
+      <c r="F957" s="1">
+        <v>0</v>
+      </c>
+      <c r="G957" s="2"/>
+      <c r="H957" s="1">
+        <v>3</v>
+      </c>
+      <c r="I957">
+        <f t="shared" si="14"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="958" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A958" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B958" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C958" s="1">
+        <v>70</v>
+      </c>
+      <c r="D958" s="1">
+        <v>9</v>
+      </c>
+      <c r="E958" s="1">
+        <v>6</v>
+      </c>
+      <c r="F958" s="1">
+        <v>0</v>
+      </c>
+      <c r="G958" s="2"/>
+      <c r="H958" s="1">
+        <v>8</v>
+      </c>
+      <c r="I958">
+        <f t="shared" si="14"/>
+        <v>630</v>
+      </c>
+    </row>
+    <row r="959" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A959" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B959" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C959" s="1">
+        <v>70</v>
+      </c>
+      <c r="D959" s="1">
+        <v>4</v>
+      </c>
+      <c r="E959" s="1">
+        <v>4</v>
+      </c>
+      <c r="F959" s="1">
+        <v>10</v>
+      </c>
+      <c r="G959" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H959" s="1">
+        <v>0</v>
+      </c>
+      <c r="I959">
+        <f t="shared" si="14"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="960" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A960" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B960" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C960" s="1">
+        <v>70</v>
+      </c>
+      <c r="D960" s="1">
+        <v>5</v>
+      </c>
+      <c r="E960" s="1">
+        <v>5</v>
+      </c>
+      <c r="F960" s="1">
+        <v>4</v>
+      </c>
+      <c r="G960" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H960" s="1">
+        <v>7</v>
+      </c>
+      <c r="I960">
+        <f t="shared" si="14"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="961" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A961" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B961" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C961" s="1">
+        <v>70</v>
+      </c>
+      <c r="D961" s="1">
+        <v>5</v>
+      </c>
+      <c r="E961" s="1">
+        <v>5</v>
+      </c>
+      <c r="F961" s="1">
+        <v>0</v>
+      </c>
+      <c r="G961" s="2"/>
+      <c r="H961" s="1">
+        <v>5</v>
+      </c>
+      <c r="I961">
+        <f t="shared" si="14"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="962" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A962" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B962" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C962" s="1">
+        <v>70</v>
+      </c>
+      <c r="D962" s="1">
+        <v>5</v>
+      </c>
+      <c r="E962" s="1">
+        <v>3</v>
+      </c>
+      <c r="F962" s="1">
+        <v>0</v>
+      </c>
+      <c r="G962" s="2"/>
+      <c r="H962" s="1">
+        <v>2</v>
+      </c>
+      <c r="I962">
+        <f t="shared" si="14"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="963" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A963" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B963" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C963" s="1">
+        <v>70</v>
+      </c>
+      <c r="D963" s="1">
+        <v>7</v>
+      </c>
+      <c r="E963" s="1">
+        <v>8</v>
+      </c>
+      <c r="F963" s="1">
+        <v>0</v>
+      </c>
+      <c r="G963" s="2"/>
+      <c r="H963" s="1">
+        <v>9</v>
+      </c>
+      <c r="I963">
+        <f t="shared" si="14"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="964" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A964" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B964" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C964" s="1">
+        <v>70</v>
+      </c>
+      <c r="D964" s="1">
+        <v>4</v>
+      </c>
+      <c r="E964" s="1">
+        <v>7</v>
+      </c>
+      <c r="F964" s="1">
+        <v>4</v>
+      </c>
+      <c r="G964" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H964" s="1">
+        <v>8</v>
+      </c>
+      <c r="I964">
+        <f t="shared" ref="I964:I966" si="15">C964*D964</f>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="965" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A965" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B965" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C965" s="1">
+        <v>70</v>
+      </c>
+      <c r="D965" s="1">
+        <v>7</v>
+      </c>
+      <c r="E965" s="1">
+        <v>7</v>
+      </c>
+      <c r="F965" s="1">
+        <v>0</v>
+      </c>
+      <c r="G965" s="2"/>
+      <c r="H965" s="1">
+        <v>3</v>
+      </c>
+      <c r="I965">
+        <f t="shared" si="15"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="966" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A966" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B966" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C966" s="1">
+        <v>70</v>
+      </c>
+      <c r="D966" s="1">
+        <v>4</v>
+      </c>
+      <c r="E966" s="1">
+        <v>6</v>
+      </c>
+      <c r="F966" s="1">
+        <v>3</v>
+      </c>
+      <c r="G966" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H966" s="1">
+        <v>4</v>
+      </c>
+      <c r="I966">
+        <f t="shared" si="15"/>
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/data/Wellness.xlsx
+++ b/data/Wellness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6E6C04-1C33-924B-A3EF-497C29B72667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A03311D-550F-9545-901D-1FF352EF40B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{1A9C3045-D9B1-2C40-BB1C-55E131BFBA85}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="163">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -522,6 +522,9 @@
   </si>
   <si>
     <t>Tibia </t>
+  </si>
+  <si>
+    <t>Ischio cheville </t>
   </si>
 </sst>
 </file>
@@ -1314,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D0374B-10DC-0242-BBAD-60229EC6B28B}">
-  <dimension ref="A1:I966"/>
+  <dimension ref="A1:I996"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
@@ -29370,7 +29373,7 @@
         <v>8</v>
       </c>
       <c r="I964">
-        <f t="shared" ref="I964:I966" si="15">C964*D964</f>
+        <f t="shared" ref="I964:I996" si="15">C964*D964</f>
         <v>280</v>
       </c>
     </row>
@@ -29430,6 +29433,878 @@
       <c r="I966">
         <f t="shared" si="15"/>
         <v>280</v>
+      </c>
+    </row>
+    <row r="967" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A967" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B967" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C967" s="1">
+        <v>70</v>
+      </c>
+      <c r="D967" s="1">
+        <v>4</v>
+      </c>
+      <c r="E967" s="1">
+        <v>6</v>
+      </c>
+      <c r="F967" s="1">
+        <v>3</v>
+      </c>
+      <c r="G967" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H967" s="1">
+        <v>4</v>
+      </c>
+      <c r="I967">
+        <f t="shared" si="15"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="968" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A968" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B968" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C968" s="1">
+        <v>70</v>
+      </c>
+      <c r="D968" s="1">
+        <v>7</v>
+      </c>
+      <c r="E968" s="1">
+        <v>7</v>
+      </c>
+      <c r="F968" s="1">
+        <v>3</v>
+      </c>
+      <c r="G968" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H968" s="1">
+        <v>10</v>
+      </c>
+      <c r="I968">
+        <f t="shared" si="15"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="969" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A969" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B969" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C969" s="1">
+        <v>70</v>
+      </c>
+      <c r="D969" s="1">
+        <v>6</v>
+      </c>
+      <c r="E969" s="1">
+        <v>5</v>
+      </c>
+      <c r="F969" s="1">
+        <v>0</v>
+      </c>
+      <c r="G969" s="2"/>
+      <c r="H969" s="1">
+        <v>9</v>
+      </c>
+      <c r="I969">
+        <f t="shared" si="15"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="970" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A970" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B970" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C970" s="1">
+        <v>70</v>
+      </c>
+      <c r="D970" s="1">
+        <v>5</v>
+      </c>
+      <c r="E970" s="1">
+        <v>3</v>
+      </c>
+      <c r="F970" s="1">
+        <v>3</v>
+      </c>
+      <c r="G970" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H970" s="1">
+        <v>3</v>
+      </c>
+      <c r="I970">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="971" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A971" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B971" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C971" s="1">
+        <v>70</v>
+      </c>
+      <c r="D971" s="1">
+        <v>5</v>
+      </c>
+      <c r="E971" s="1">
+        <v>5</v>
+      </c>
+      <c r="F971" s="1">
+        <v>0</v>
+      </c>
+      <c r="G971" s="2"/>
+      <c r="H971" s="1">
+        <v>8</v>
+      </c>
+      <c r="I971">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="972" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A972" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B972" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C972" s="1">
+        <v>70</v>
+      </c>
+      <c r="D972" s="1">
+        <v>4</v>
+      </c>
+      <c r="E972" s="1">
+        <v>6</v>
+      </c>
+      <c r="F972" s="1">
+        <v>6</v>
+      </c>
+      <c r="G972" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H972" s="1">
+        <v>9</v>
+      </c>
+      <c r="I972">
+        <f t="shared" si="15"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="973" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A973" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B973" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C973" s="1">
+        <v>70</v>
+      </c>
+      <c r="D973" s="1">
+        <v>6</v>
+      </c>
+      <c r="E973" s="1">
+        <v>5</v>
+      </c>
+      <c r="F973" s="1">
+        <v>0</v>
+      </c>
+      <c r="G973" s="2"/>
+      <c r="H973" s="1">
+        <v>9</v>
+      </c>
+      <c r="I973">
+        <f t="shared" si="15"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="974" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A974" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B974" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C974" s="1">
+        <v>70</v>
+      </c>
+      <c r="D974" s="1">
+        <v>7</v>
+      </c>
+      <c r="E974" s="1">
+        <v>5</v>
+      </c>
+      <c r="F974" s="1">
+        <v>0</v>
+      </c>
+      <c r="G974" s="2"/>
+      <c r="H974" s="1">
+        <v>0</v>
+      </c>
+      <c r="I974">
+        <f t="shared" si="15"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="975" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A975" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B975" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C975" s="1">
+        <v>70</v>
+      </c>
+      <c r="D975" s="1">
+        <v>6</v>
+      </c>
+      <c r="E975" s="1">
+        <v>6</v>
+      </c>
+      <c r="F975" s="1">
+        <v>6</v>
+      </c>
+      <c r="G975" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H975" s="1">
+        <v>5</v>
+      </c>
+      <c r="I975">
+        <f t="shared" si="15"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="976" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A976" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B976" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C976" s="1">
+        <v>70</v>
+      </c>
+      <c r="D976" s="1">
+        <v>5</v>
+      </c>
+      <c r="E976" s="1">
+        <v>4</v>
+      </c>
+      <c r="F976" s="1">
+        <v>6</v>
+      </c>
+      <c r="G976" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H976" s="1">
+        <v>7</v>
+      </c>
+      <c r="I976">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="977" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A977" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B977" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C977" s="1">
+        <v>70</v>
+      </c>
+      <c r="D977" s="1">
+        <v>5</v>
+      </c>
+      <c r="E977" s="1">
+        <v>5</v>
+      </c>
+      <c r="F977" s="1">
+        <v>0</v>
+      </c>
+      <c r="G977" s="2"/>
+      <c r="H977" s="1">
+        <v>8</v>
+      </c>
+      <c r="I977">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="978" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A978" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B978" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C978" s="1">
+        <v>70</v>
+      </c>
+      <c r="D978" s="1">
+        <v>7</v>
+      </c>
+      <c r="E978" s="1">
+        <v>6</v>
+      </c>
+      <c r="F978" s="1">
+        <v>4</v>
+      </c>
+      <c r="G978" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H978" s="1">
+        <v>2</v>
+      </c>
+      <c r="I978">
+        <f t="shared" si="15"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="979" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A979" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B979" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C979" s="1">
+        <v>70</v>
+      </c>
+      <c r="D979" s="1">
+        <v>7</v>
+      </c>
+      <c r="E979" s="1">
+        <v>6</v>
+      </c>
+      <c r="F979" s="1">
+        <v>0</v>
+      </c>
+      <c r="G979" s="2"/>
+      <c r="H979" s="1">
+        <v>5</v>
+      </c>
+      <c r="I979">
+        <f t="shared" si="15"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="980" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A980" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B980" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C980" s="1">
+        <v>70</v>
+      </c>
+      <c r="D980" s="1">
+        <v>6</v>
+      </c>
+      <c r="E980" s="1">
+        <v>6</v>
+      </c>
+      <c r="F980" s="1">
+        <v>7</v>
+      </c>
+      <c r="G980" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H980" s="1">
+        <v>0</v>
+      </c>
+      <c r="I980">
+        <f t="shared" si="15"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="981" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A981" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B981" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C981" s="1">
+        <v>70</v>
+      </c>
+      <c r="D981" s="1">
+        <v>4</v>
+      </c>
+      <c r="E981" s="1">
+        <v>5</v>
+      </c>
+      <c r="F981" s="1">
+        <v>3</v>
+      </c>
+      <c r="G981" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H981" s="1">
+        <v>8</v>
+      </c>
+      <c r="I981">
+        <f t="shared" si="15"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="982" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A982" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B982" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C982" s="1">
+        <v>70</v>
+      </c>
+      <c r="D982" s="1">
+        <v>5</v>
+      </c>
+      <c r="E982" s="1">
+        <v>5</v>
+      </c>
+      <c r="F982" s="1">
+        <v>2</v>
+      </c>
+      <c r="G982" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H982" s="1">
+        <v>5</v>
+      </c>
+      <c r="I982">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="983" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A983" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B983" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C983" s="1">
+        <v>70</v>
+      </c>
+      <c r="D983" s="1">
+        <v>5</v>
+      </c>
+      <c r="E983" s="1">
+        <v>3</v>
+      </c>
+      <c r="F983" s="1">
+        <v>0</v>
+      </c>
+      <c r="G983" s="2"/>
+      <c r="H983" s="1">
+        <v>5</v>
+      </c>
+      <c r="I983">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="984" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A984" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B984" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C984" s="1">
+        <v>70</v>
+      </c>
+      <c r="D984" s="1">
+        <v>4</v>
+      </c>
+      <c r="E984" s="1">
+        <v>3</v>
+      </c>
+      <c r="F984" s="1">
+        <v>3</v>
+      </c>
+      <c r="G984" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H984" s="1">
+        <v>2</v>
+      </c>
+      <c r="I984">
+        <f t="shared" si="15"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="985" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A985" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B985" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C985" s="1">
+        <v>70</v>
+      </c>
+      <c r="D985" s="1">
+        <v>2</v>
+      </c>
+      <c r="E985" s="1">
+        <v>6</v>
+      </c>
+      <c r="F985" s="1">
+        <v>6</v>
+      </c>
+      <c r="G985" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H985" s="1">
+        <v>2</v>
+      </c>
+      <c r="I985">
+        <f t="shared" si="15"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="986" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A986" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B986" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C986" s="1">
+        <v>70</v>
+      </c>
+      <c r="D986" s="1">
+        <v>6</v>
+      </c>
+      <c r="E986" s="1">
+        <v>6</v>
+      </c>
+      <c r="F986" s="1">
+        <v>0</v>
+      </c>
+      <c r="G986" s="2"/>
+      <c r="H986" s="1">
+        <v>6</v>
+      </c>
+      <c r="I986">
+        <f t="shared" si="15"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="987" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A987" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B987" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C987" s="1">
+        <v>70</v>
+      </c>
+      <c r="D987" s="1">
+        <v>7</v>
+      </c>
+      <c r="E987" s="1">
+        <v>6</v>
+      </c>
+      <c r="F987" s="1">
+        <v>0</v>
+      </c>
+      <c r="G987" s="2"/>
+      <c r="H987" s="1">
+        <v>1</v>
+      </c>
+      <c r="I987">
+        <f t="shared" si="15"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="988" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A988" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B988" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C988" s="1">
+        <v>70</v>
+      </c>
+      <c r="D988" s="1">
+        <v>5</v>
+      </c>
+      <c r="E988" s="1">
+        <v>5</v>
+      </c>
+      <c r="F988" s="1">
+        <v>6</v>
+      </c>
+      <c r="G988" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H988" s="1">
+        <v>0</v>
+      </c>
+      <c r="I988">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="989" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A989" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B989" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C989" s="1">
+        <v>70</v>
+      </c>
+      <c r="D989" s="1">
+        <v>5</v>
+      </c>
+      <c r="E989" s="1">
+        <v>5</v>
+      </c>
+      <c r="F989" s="1">
+        <v>0</v>
+      </c>
+      <c r="G989" s="2"/>
+      <c r="H989" s="1">
+        <v>1</v>
+      </c>
+      <c r="I989">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="990" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A990" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B990" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C990" s="1">
+        <v>70</v>
+      </c>
+      <c r="D990" s="1">
+        <v>5</v>
+      </c>
+      <c r="E990" s="1">
+        <v>7</v>
+      </c>
+      <c r="F990" s="1">
+        <v>3</v>
+      </c>
+      <c r="G990" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H990" s="1">
+        <v>0</v>
+      </c>
+      <c r="I990">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="991" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A991" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B991" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C991" s="1">
+        <v>70</v>
+      </c>
+      <c r="D991" s="1">
+        <v>4</v>
+      </c>
+      <c r="E991" s="1">
+        <v>3</v>
+      </c>
+      <c r="F991" s="1">
+        <v>0</v>
+      </c>
+      <c r="G991" s="2"/>
+      <c r="H991" s="1">
+        <v>8</v>
+      </c>
+      <c r="I991">
+        <f t="shared" si="15"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="992" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A992" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B992" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C992" s="1">
+        <v>70</v>
+      </c>
+      <c r="D992" s="1">
+        <v>4</v>
+      </c>
+      <c r="E992" s="1">
+        <v>3</v>
+      </c>
+      <c r="F992" s="1">
+        <v>5</v>
+      </c>
+      <c r="G992" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H992" s="1">
+        <v>3</v>
+      </c>
+      <c r="I992">
+        <f t="shared" si="15"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="993" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A993" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B993" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C993" s="1">
+        <v>70</v>
+      </c>
+      <c r="D993" s="1">
+        <v>6</v>
+      </c>
+      <c r="E993" s="1">
+        <v>6</v>
+      </c>
+      <c r="F993" s="1">
+        <v>0</v>
+      </c>
+      <c r="G993" s="2"/>
+      <c r="H993" s="1">
+        <v>6</v>
+      </c>
+      <c r="I993">
+        <f t="shared" si="15"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="994" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A994" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B994" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C994" s="1">
+        <v>70</v>
+      </c>
+      <c r="D994" s="1">
+        <v>4</v>
+      </c>
+      <c r="E994" s="1">
+        <v>0</v>
+      </c>
+      <c r="F994" s="1">
+        <v>0</v>
+      </c>
+      <c r="G994" s="2"/>
+      <c r="H994" s="1">
+        <v>3</v>
+      </c>
+      <c r="I994">
+        <f t="shared" si="15"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="995" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A995" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B995" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C995" s="1">
+        <v>70</v>
+      </c>
+      <c r="D995" s="1">
+        <v>4</v>
+      </c>
+      <c r="E995" s="1">
+        <v>3</v>
+      </c>
+      <c r="F995" s="1">
+        <v>0</v>
+      </c>
+      <c r="G995" s="2"/>
+      <c r="H995" s="1">
+        <v>2</v>
+      </c>
+      <c r="I995">
+        <f t="shared" si="15"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="996" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A996" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B996" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C996" s="1">
+        <v>70</v>
+      </c>
+      <c r="D996" s="1">
+        <v>5</v>
+      </c>
+      <c r="E996" s="1">
+        <v>5</v>
+      </c>
+      <c r="F996" s="1">
+        <v>8</v>
+      </c>
+      <c r="G996" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H996" s="1">
+        <v>2</v>
+      </c>
+      <c r="I996">
+        <f t="shared" si="15"/>
+        <v>350</v>
       </c>
     </row>
   </sheetData>

--- a/data/Wellness.xlsx
+++ b/data/Wellness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A03311D-550F-9545-901D-1FF352EF40B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2663D50B-4496-DE42-B37F-E78BFADD5E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{1A9C3045-D9B1-2C40-BB1C-55E131BFBA85}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="166">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -525,6 +525,15 @@
   </si>
   <si>
     <t>Ischio cheville </t>
+  </si>
+  <si>
+    <t>Genou mollet</t>
+  </si>
+  <si>
+    <t>Ishio</t>
+  </si>
+  <si>
+    <t>Épaule </t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D0374B-10DC-0242-BBAD-60229EC6B28B}">
-  <dimension ref="A1:I996"/>
+  <dimension ref="A1:I1023"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
@@ -29373,7 +29382,7 @@
         <v>8</v>
       </c>
       <c r="I964">
-        <f t="shared" ref="I964:I996" si="15">C964*D964</f>
+        <f t="shared" ref="I964:I1023" si="15">C964*D964</f>
         <v>280</v>
       </c>
     </row>
@@ -30305,6 +30314,792 @@
       <c r="I996">
         <f t="shared" si="15"/>
         <v>350</v>
+      </c>
+    </row>
+    <row r="997" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A997" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B997" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C997" s="1">
+        <v>70</v>
+      </c>
+      <c r="D997" s="1">
+        <v>7</v>
+      </c>
+      <c r="E997" s="1">
+        <v>6</v>
+      </c>
+      <c r="F997" s="1">
+        <v>3</v>
+      </c>
+      <c r="G997" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H997" s="1">
+        <v>3</v>
+      </c>
+      <c r="I997">
+        <f t="shared" si="15"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="998" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A998" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B998" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C998" s="1">
+        <v>70</v>
+      </c>
+      <c r="D998" s="1">
+        <v>6</v>
+      </c>
+      <c r="E998" s="1">
+        <v>5</v>
+      </c>
+      <c r="F998" s="1">
+        <v>0</v>
+      </c>
+      <c r="G998" s="2"/>
+      <c r="H998" s="1">
+        <v>8</v>
+      </c>
+      <c r="I998">
+        <f t="shared" si="15"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="999" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A999" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B999" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C999" s="1">
+        <v>70</v>
+      </c>
+      <c r="D999" s="1">
+        <v>7</v>
+      </c>
+      <c r="E999" s="1">
+        <v>5</v>
+      </c>
+      <c r="F999" s="1">
+        <v>0</v>
+      </c>
+      <c r="G999" s="2"/>
+      <c r="H999" s="1">
+        <v>8</v>
+      </c>
+      <c r="I999">
+        <f t="shared" si="15"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1000" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B1000" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1000" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1000" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1000" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1000" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1000" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1000" s="1">
+        <v>5</v>
+      </c>
+      <c r="I1000">
+        <f t="shared" si="15"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1001" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B1001" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1001" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1001" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1001" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1001" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1001" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H1001" s="1">
+        <v>9</v>
+      </c>
+      <c r="I1001">
+        <f t="shared" si="15"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1002" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B1002" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1002" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1002" s="1">
+        <v>8</v>
+      </c>
+      <c r="E1002" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1002" s="1">
+        <v>2</v>
+      </c>
+      <c r="G1002" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1002" s="1">
+        <v>9</v>
+      </c>
+      <c r="I1002">
+        <f t="shared" si="15"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1003" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B1003" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1003" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1003" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1003" s="1">
+        <v>2</v>
+      </c>
+      <c r="F1003" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1003" s="2"/>
+      <c r="H1003" s="1">
+        <v>2</v>
+      </c>
+      <c r="I1003">
+        <f t="shared" si="15"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1004" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B1004" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1004" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1004" s="1">
+        <v>8</v>
+      </c>
+      <c r="E1004" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1004" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1004" s="2"/>
+      <c r="H1004" s="1">
+        <v>10</v>
+      </c>
+      <c r="I1004">
+        <f t="shared" si="15"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1005" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B1005" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1005" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1005" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1005" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1005" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1005" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1005" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1005">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1006" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B1006" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1006" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1006" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1006" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1006" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1006" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1006" s="1">
+        <v>10</v>
+      </c>
+      <c r="I1006">
+        <f t="shared" si="15"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1007" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B1007" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1007" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1007" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1007" s="1">
+        <v>5</v>
+      </c>
+      <c r="F1007" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1007" s="2"/>
+      <c r="H1007" s="1">
+        <v>2</v>
+      </c>
+      <c r="I1007">
+        <f t="shared" si="15"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1008" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B1008" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1008" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1008" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1008" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1008" s="1">
+        <v>3</v>
+      </c>
+      <c r="G1008" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1008" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1008">
+        <f t="shared" si="15"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1009" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B1009" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1009" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1009" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1009" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1009" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1009" s="2"/>
+      <c r="H1009" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1009">
+        <f t="shared" si="15"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1010" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B1010" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1010" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1010" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1010" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1010" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1010" s="2"/>
+      <c r="H1010" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1010">
+        <f t="shared" si="15"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1011" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B1011" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1011" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1011" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1011" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1011" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1011" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1011" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1011">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1012" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B1012" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1012" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1012" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1012" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1012" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1012" s="2"/>
+      <c r="H1012" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1012">
+        <f t="shared" si="15"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1013" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B1013" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1013" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1013" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1013" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1013" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1013" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1013" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1013">
+        <f t="shared" si="15"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1014" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B1014" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1014" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1014" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1014" s="1">
+        <v>5</v>
+      </c>
+      <c r="F1014" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1014" s="2"/>
+      <c r="H1014" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1014">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1015" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B1015" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1015" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1015" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1015" s="1">
+        <v>5</v>
+      </c>
+      <c r="F1015" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1015" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H1015" s="1">
+        <v>2</v>
+      </c>
+      <c r="I1015">
+        <f t="shared" si="15"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1016" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B1016" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1016" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1016" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1016" s="1">
+        <v>5</v>
+      </c>
+      <c r="F1016" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1016" s="2"/>
+      <c r="H1016" s="1">
+        <v>5</v>
+      </c>
+      <c r="I1016">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1017" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B1017" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1017" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1017" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1017" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1017" s="1">
+        <v>3</v>
+      </c>
+      <c r="G1017" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1017" s="1">
+        <v>5</v>
+      </c>
+      <c r="I1017">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1018" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B1018" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1018" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1018" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1018" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1018" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1018" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1018" s="1">
+        <v>10</v>
+      </c>
+      <c r="I1018">
+        <f t="shared" si="15"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1019" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B1019" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1019" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1019" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1019" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1019" s="1">
+        <v>3</v>
+      </c>
+      <c r="G1019" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1019" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1019">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1020" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B1020" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1020" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1020" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1020" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1020" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1020" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1020" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1020">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1021" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B1021" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1021" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1021" s="1">
+        <v>8</v>
+      </c>
+      <c r="E1021" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1021" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1021" s="2"/>
+      <c r="H1021" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1021">
+        <f t="shared" si="15"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1022" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B1022" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1022" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1022" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1022" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1022" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1022" s="2"/>
+      <c r="H1022" s="1">
+        <v>5</v>
+      </c>
+      <c r="I1022">
+        <f t="shared" si="15"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1023" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B1023" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1023" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1023" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1023" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1023" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1023" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1023" s="1">
+        <v>10</v>
+      </c>
+      <c r="I1023">
+        <f t="shared" si="15"/>
+        <v>490</v>
       </c>
     </row>
   </sheetData>

--- a/data/Wellness.xlsx
+++ b/data/Wellness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2663D50B-4496-DE42-B37F-E78BFADD5E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46E431C-A022-A647-AFBF-4065AF804275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{1A9C3045-D9B1-2C40-BB1C-55E131BFBA85}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="169">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -534,6 +534,15 @@
   </si>
   <si>
     <t>Épaule </t>
+  </si>
+  <si>
+    <t>Quadri bequille</t>
+  </si>
+  <si>
+    <t>Genou coup</t>
+  </si>
+  <si>
+    <t>Pied </t>
   </si>
 </sst>
 </file>
@@ -1326,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D0374B-10DC-0242-BBAD-60229EC6B28B}">
-  <dimension ref="A1:I1023"/>
+  <dimension ref="A1:I1049"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
@@ -29382,7 +29391,7 @@
         <v>8</v>
       </c>
       <c r="I964">
-        <f t="shared" ref="I964:I1023" si="15">C964*D964</f>
+        <f t="shared" ref="I964:I1027" si="15">C964*D964</f>
         <v>280</v>
       </c>
     </row>
@@ -31100,6 +31109,768 @@
       <c r="I1023">
         <f t="shared" si="15"/>
         <v>490</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1024" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B1024" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1024" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1024" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1024" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1024" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1024" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1024" s="1">
+        <v>2</v>
+      </c>
+      <c r="I1024">
+        <f t="shared" si="15"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1025" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B1025" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1025" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1025" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1025" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1025" s="1">
+        <v>3</v>
+      </c>
+      <c r="G1025" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1025" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1025">
+        <f t="shared" si="15"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1026" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B1026" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1026" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1026" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1026" s="1">
+        <v>5</v>
+      </c>
+      <c r="F1026" s="1">
+        <v>2</v>
+      </c>
+      <c r="G1026" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1026" s="1">
+        <v>9</v>
+      </c>
+      <c r="I1026">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1027" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B1027" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1027" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1027" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1027" s="1">
+        <v>5</v>
+      </c>
+      <c r="F1027" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1027" s="2"/>
+      <c r="H1027" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1027">
+        <f t="shared" si="15"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1028" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B1028" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1028" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1028" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1028" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1028" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1028" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H1028" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1028">
+        <f t="shared" ref="I1028:I1049" si="16">C1028*D1028</f>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1029" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B1029" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1029" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1029" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1029" s="1">
+        <v>5</v>
+      </c>
+      <c r="F1029" s="1">
+        <v>2</v>
+      </c>
+      <c r="G1029" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1029" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1029">
+        <f t="shared" si="16"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1030" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B1030" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1030" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1030" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1030" s="1">
+        <v>3</v>
+      </c>
+      <c r="F1030" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1030" s="2"/>
+      <c r="H1030" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1030">
+        <f t="shared" si="16"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1031" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B1031" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1031" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1031" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1031" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1031" s="1">
+        <v>3</v>
+      </c>
+      <c r="G1031" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1031" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1031">
+        <f t="shared" si="16"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1032" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B1032" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1032" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1032" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1032" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1032" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1032" s="2"/>
+      <c r="H1032" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1032">
+        <f t="shared" si="16"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1033" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B1033" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1033" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1033" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1033" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1033" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1033" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1033" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1033">
+        <f t="shared" si="16"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1034" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B1034" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1034" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1034" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1034" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1034" s="1">
+        <v>3</v>
+      </c>
+      <c r="G1034" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1034" s="1">
+        <v>3</v>
+      </c>
+      <c r="I1034">
+        <f t="shared" si="16"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1035" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B1035" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1035" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1035" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1035" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1035" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1035" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1035" s="1">
+        <v>6</v>
+      </c>
+      <c r="I1035">
+        <f t="shared" si="16"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1036" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B1036" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1036" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1036" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1036" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1036" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1036" s="2"/>
+      <c r="H1036" s="1">
+        <v>10</v>
+      </c>
+      <c r="I1036">
+        <f t="shared" si="16"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1037" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B1037" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1037" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1037" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1037" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1037" s="1">
+        <v>2</v>
+      </c>
+      <c r="G1037" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1037" s="1">
+        <v>5</v>
+      </c>
+      <c r="I1037">
+        <f t="shared" si="16"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1038" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B1038" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1038" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1038" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1038" s="1">
+        <v>5</v>
+      </c>
+      <c r="F1038" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1038" s="2"/>
+      <c r="H1038" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1038">
+        <f t="shared" si="16"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1039" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B1039" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1039" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1039" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1039" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1039" s="1">
+        <v>2</v>
+      </c>
+      <c r="G1039" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1039" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1039">
+        <f t="shared" si="16"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1040" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B1040" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1040" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1040" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1040" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1040" s="1">
+        <v>2</v>
+      </c>
+      <c r="G1040" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1040" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1040">
+        <f t="shared" si="16"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1041" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B1041" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1041" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1041" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1041" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1041" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1041" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1041" s="1">
+        <v>3</v>
+      </c>
+      <c r="I1041">
+        <f t="shared" si="16"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1042" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B1042" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1042" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1042" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1042" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1042" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1042" s="2"/>
+      <c r="H1042" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1042">
+        <f t="shared" si="16"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1043" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B1043" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1043" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1043" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1043" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1043" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1043" s="2"/>
+      <c r="H1043" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1043">
+        <f t="shared" si="16"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1044" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B1044" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1044" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1044" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1044" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1044" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1044" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1044" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1044">
+        <f t="shared" si="16"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1045" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B1045" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1045" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1045" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1045" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1045" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1045" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1045" s="1">
+        <v>10</v>
+      </c>
+      <c r="I1045">
+        <f t="shared" si="16"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1046" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B1046" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1046" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1046" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1046" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1046" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1046" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1046" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1046">
+        <f t="shared" si="16"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1047" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B1047" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1047" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1047" s="1">
+        <v>8</v>
+      </c>
+      <c r="E1047" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1047" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1047" s="2"/>
+      <c r="H1047" s="1">
+        <v>5</v>
+      </c>
+      <c r="I1047">
+        <f t="shared" si="16"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1048" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B1048" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1048" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1048" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1048" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1048" s="1">
+        <v>2</v>
+      </c>
+      <c r="G1048" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1048" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1048">
+        <f t="shared" si="16"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1049" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B1049" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1049" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1049" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1049" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1049" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1049" s="2"/>
+      <c r="H1049" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1049">
+        <f t="shared" si="16"/>
+        <v>350</v>
       </c>
     </row>
   </sheetData>

--- a/data/Wellness.xlsx
+++ b/data/Wellness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46E431C-A022-A647-AFBF-4065AF804275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22C3063-897E-B84C-A414-EEF903FF9067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{1A9C3045-D9B1-2C40-BB1C-55E131BFBA85}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="170">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -543,6 +543,9 @@
   </si>
   <si>
     <t>Pied </t>
+  </si>
+  <si>
+    <t>Genou béquille </t>
   </si>
 </sst>
 </file>
@@ -1335,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D0374B-10DC-0242-BBAD-60229EC6B28B}">
-  <dimension ref="A1:I1049"/>
+  <dimension ref="A1:I1059"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
@@ -31255,7 +31258,7 @@
         <v>8</v>
       </c>
       <c r="I1028">
-        <f t="shared" ref="I1028:I1049" si="16">C1028*D1028</f>
+        <f t="shared" ref="I1028:I1059" si="16">C1028*D1028</f>
         <v>280</v>
       </c>
     </row>
@@ -31869,6 +31872,300 @@
         <v>8</v>
       </c>
       <c r="I1049">
+        <f t="shared" si="16"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1050" s="3">
+        <v>46119</v>
+      </c>
+      <c r="B1050" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1050" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1050" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1050" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1050" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1050" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1050" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1050">
+        <f t="shared" si="16"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1051" s="3">
+        <v>46119</v>
+      </c>
+      <c r="B1051" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1051" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1051" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1051" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1051" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1051" s="2"/>
+      <c r="H1051" s="1">
+        <v>9</v>
+      </c>
+      <c r="I1051">
+        <f t="shared" si="16"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1052" s="3">
+        <v>46119</v>
+      </c>
+      <c r="B1052" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1052" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1052" s="1">
+        <v>8</v>
+      </c>
+      <c r="E1052" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1052" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1052" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1052" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1052">
+        <f t="shared" si="16"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1053" s="3">
+        <v>46119</v>
+      </c>
+      <c r="B1053" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1053" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1053" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1053" s="1">
+        <v>5</v>
+      </c>
+      <c r="F1053" s="1">
+        <v>2</v>
+      </c>
+      <c r="G1053" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1053" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1053">
+        <f t="shared" si="16"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1054" s="3">
+        <v>46119</v>
+      </c>
+      <c r="B1054" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1054" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1054" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1054" s="1">
+        <v>10</v>
+      </c>
+      <c r="F1054" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1054" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1054" s="1">
+        <v>3</v>
+      </c>
+      <c r="I1054">
+        <f t="shared" si="16"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1055" s="3">
+        <v>46119</v>
+      </c>
+      <c r="B1055" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1055" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1055" s="1">
+        <v>8</v>
+      </c>
+      <c r="E1055" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1055" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1055" s="2"/>
+      <c r="H1055" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1055">
+        <f t="shared" si="16"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1056" s="3">
+        <v>46119</v>
+      </c>
+      <c r="B1056" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1056" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1056" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1056" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1056" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1056" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1056" s="1">
+        <v>3</v>
+      </c>
+      <c r="I1056">
+        <f t="shared" si="16"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1057" s="3">
+        <v>46119</v>
+      </c>
+      <c r="B1057" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1057" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1057" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1057" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1057" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1057" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H1057" s="1">
+        <v>10</v>
+      </c>
+      <c r="I1057">
+        <f t="shared" si="16"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1058" s="3">
+        <v>46119</v>
+      </c>
+      <c r="B1058" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1058" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1058" s="1">
+        <v>8</v>
+      </c>
+      <c r="E1058" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1058" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1058" s="2"/>
+      <c r="H1058" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1058">
+        <f t="shared" si="16"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1059" s="3">
+        <v>46119</v>
+      </c>
+      <c r="B1059" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1059" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1059" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1059" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1059" s="1">
+        <v>3</v>
+      </c>
+      <c r="G1059" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1059" s="1">
+        <v>6</v>
+      </c>
+      <c r="I1059">
         <f t="shared" si="16"/>
         <v>350</v>
       </c>

--- a/data/Wellness.xlsx
+++ b/data/Wellness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22C3063-897E-B84C-A414-EEF903FF9067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EADCC25-C0DA-3B4C-9CA2-FBEB7B4D9E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{1A9C3045-D9B1-2C40-BB1C-55E131BFBA85}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="170">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -1338,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D0374B-10DC-0242-BBAD-60229EC6B28B}">
-  <dimension ref="A1:I1059"/>
+  <dimension ref="A1:I1069"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
@@ -31258,7 +31258,7 @@
         <v>8</v>
       </c>
       <c r="I1028">
-        <f t="shared" ref="I1028:I1059" si="16">C1028*D1028</f>
+        <f t="shared" ref="I1028:I1069" si="16">C1028*D1028</f>
         <v>280</v>
       </c>
     </row>
@@ -32168,6 +32168,296 @@
       <c r="I1059">
         <f t="shared" si="16"/>
         <v>350</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1060" s="3">
+        <v>46120</v>
+      </c>
+      <c r="B1060" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1060" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1060" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1060" s="1">
+        <v>5</v>
+      </c>
+      <c r="F1060" s="1">
+        <v>2</v>
+      </c>
+      <c r="G1060" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1060" s="1">
+        <v>9</v>
+      </c>
+      <c r="I1060">
+        <f t="shared" si="16"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1061" s="3">
+        <v>46120</v>
+      </c>
+      <c r="B1061" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1061" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1061" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1061" s="1">
+        <v>3</v>
+      </c>
+      <c r="F1061" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1061" s="2"/>
+      <c r="H1061" s="1">
+        <v>6</v>
+      </c>
+      <c r="I1061">
+        <f t="shared" si="16"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1062" s="3">
+        <v>46120</v>
+      </c>
+      <c r="B1062" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1062" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1062" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1062" s="1">
+        <v>3</v>
+      </c>
+      <c r="F1062" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1062" s="2"/>
+      <c r="H1062" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1062">
+        <f t="shared" si="16"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1063" s="3">
+        <v>46120</v>
+      </c>
+      <c r="B1063" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1063" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1063" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1063" s="1">
+        <v>5</v>
+      </c>
+      <c r="F1063" s="1">
+        <v>2</v>
+      </c>
+      <c r="G1063" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1063" s="1">
+        <v>6</v>
+      </c>
+      <c r="I1063">
+        <f t="shared" si="16"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1064" s="3">
+        <v>46120</v>
+      </c>
+      <c r="B1064" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1064" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1064" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1064" s="1">
+        <v>9</v>
+      </c>
+      <c r="F1064" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1064" s="2"/>
+      <c r="H1064" s="1">
+        <v>6</v>
+      </c>
+      <c r="I1064">
+        <f t="shared" si="16"/>
+        <v>630</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1065" s="3">
+        <v>46120</v>
+      </c>
+      <c r="B1065" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1065" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1065" s="1">
+        <v>8</v>
+      </c>
+      <c r="E1065" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1065" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1065" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H1065" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1065">
+        <f t="shared" si="16"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1066" s="3">
+        <v>46120</v>
+      </c>
+      <c r="B1066" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1066" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1066" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1066" s="1">
+        <v>6</v>
+      </c>
+      <c r="F1066" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1066" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1066" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1066">
+        <f t="shared" si="16"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1067" s="3">
+        <v>46120</v>
+      </c>
+      <c r="B1067" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1067" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1067" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1067" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1067" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1067" s="2"/>
+      <c r="H1067" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1067">
+        <f t="shared" si="16"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1068" s="3">
+        <v>46120</v>
+      </c>
+      <c r="B1068" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1068" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1068" s="1">
+        <v>8</v>
+      </c>
+      <c r="E1068" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1068" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1068" s="2"/>
+      <c r="H1068" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1068">
+        <f t="shared" si="16"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1069" s="3">
+        <v>46120</v>
+      </c>
+      <c r="B1069" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1069" s="1">
+        <v>70</v>
+      </c>
+      <c r="D1069" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1069" s="1">
+        <v>7</v>
+      </c>
+      <c r="F1069" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1069" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1069" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1069">
+        <f t="shared" si="16"/>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
